--- a/dados/sao_paulo/sao_paulo.xlsx
+++ b/dados/sao_paulo/sao_paulo.xlsx
@@ -8,27 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Contrato\Downloads\Data Dealer\automacao-nfs\dados\sao_paulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA133B4-7A3E-4829-A2A2-17BB531DE0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C7D72D-33AB-460B-A5CB-C273DF58C1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1EA83C79-E727-4353-BA41-A0A665306418}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -37,9 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>https://nfe.prefeitura.sp.gov.br/login.aspx</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Data de Emissão</t>
+  </si>
+  <si>
+    <t>Valor</t>
   </si>
   <si>
     <t>Nome da Empresa</t>
@@ -51,31 +45,64 @@
     <t>Certificado Digital .PFX</t>
   </si>
   <si>
-    <t>Senha do Certificado</t>
-  </si>
-  <si>
-    <t>Tomador</t>
-  </si>
-  <si>
-    <t>CJPJ Tomador</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Local da Prestação</t>
+    <t>Senha da Certidão</t>
+  </si>
+  <si>
+    <t>CNPJ Tomador</t>
+  </si>
+  <si>
+    <t>Observação</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>08/04/2026 17:15</t>
   </si>
   <si>
     <t>VALERIA MANEGEMENT</t>
   </si>
   <si>
-    <t>URL do Sistema</t>
+    <t>./dados/sao_paulo/certidoes/VALERIA CRISTINA DE PADUA.pfx</t>
+  </si>
+  <si>
+    <t>Valeria2026</t>
+  </si>
+  <si>
+    <t>33.512.889/0001-45</t>
+  </si>
+  <si>
+    <t>08/04/2026 17:00</t>
+  </si>
+  <si>
+    <t>CAROLINA</t>
+  </si>
+  <si>
+    <t>./dados/sao_paulo/certidoes/CAROLINA BARROS.pfx</t>
+  </si>
+  <si>
+    <t>Carolina2025</t>
+  </si>
+  <si>
+    <t>54.536.709/0001-35</t>
+  </si>
+  <si>
+    <t>MANA CONSULTORIA</t>
+  </si>
+  <si>
+    <t>./dados/sao_paulo/certidoes/PAULO HENRIQUE WODEWOTZKY LTDA_60720594000137.pfx</t>
+  </si>
+  <si>
+    <t>Paulo2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="00\.000\.000\/0000\-00"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -93,14 +120,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FF374151"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,16 +155,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,17 +489,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73E7066-E55D-4594-91F3-9F4B115F5217}">
-  <dimension ref="A1:J2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="20.109375" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="81.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="20.109375" customWidth="1"/>
+    <col min="9" max="9" width="23.5546875" customWidth="1"/>
+    <col min="10" max="10" width="27.88671875" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>10</v>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -471,7 +519,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -486,17 +534,140 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="6">
+        <v>53656846000140</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="6">
+        <v>11735236000192</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="6">
+        <v>22121066000172</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="6">
+        <v>60720594000137</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="E5" s="6"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="E6" s="6"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E7" s="6"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E8" s="6"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E9" s="6"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E10" s="6"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E15" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/dados/sao_paulo/sao_paulo.xlsx
+++ b/dados/sao_paulo/sao_paulo.xlsx
@@ -1,143 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Contrato\Downloads\Data Dealer\automacao-nfs\dados\sao_paulo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C7D72D-33AB-460B-A5CB-C273DF58C1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Data de Emissão</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Nome da Empresa</t>
-  </si>
-  <si>
-    <t>CNPJ Prestador</t>
-  </si>
-  <si>
-    <t>Certificado Digital .PFX</t>
-  </si>
-  <si>
-    <t>Senha da Certidão</t>
-  </si>
-  <si>
-    <t>CNPJ Tomador</t>
-  </si>
-  <si>
-    <t>Observação</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>08/04/2026 17:15</t>
-  </si>
-  <si>
-    <t>VALERIA MANEGEMENT</t>
-  </si>
-  <si>
-    <t>./dados/sao_paulo/certidoes/VALERIA CRISTINA DE PADUA.pfx</t>
-  </si>
-  <si>
-    <t>Valeria2026</t>
-  </si>
-  <si>
-    <t>33.512.889/0001-45</t>
-  </si>
-  <si>
-    <t>08/04/2026 17:00</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>./dados/sao_paulo/certidoes/CAROLINA BARROS.pfx</t>
-  </si>
-  <si>
-    <t>Carolina2025</t>
-  </si>
-  <si>
-    <t>54.536.709/0001-35</t>
-  </si>
-  <si>
-    <t>MANA CONSULTORIA</t>
-  </si>
-  <si>
-    <t>./dados/sao_paulo/certidoes/PAULO HENRIQUE WODEWOTZKY LTDA_60720594000137.pfx</t>
-  </si>
-  <si>
-    <t>Paulo2025</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="00\.000\.000\/0000\-00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -156,40 +71,99 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -489,185 +463,248 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="81.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="20.109375" customWidth="1"/>
-    <col min="9" max="9" width="23.5546875" customWidth="1"/>
-    <col min="10" max="10" width="27.88671875" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.21875" bestFit="1" customWidth="1"/>
+    <col width="20.109375" customWidth="1" min="1" max="1"/>
+    <col width="18.109375" customWidth="1" min="2" max="3"/>
+    <col width="21" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="28.109375" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
+    <col width="81.21875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="20.109375" customWidth="1" min="7" max="8"/>
+    <col width="23.5546875" customWidth="1" min="9" max="9"/>
+    <col width="27.88671875" customWidth="1" min="10" max="10"/>
+    <col width="10.21875" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="10.21875" bestFit="1" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Data de Emissão</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Nome da Empresa</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>CNPJ Prestador</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Certificado Digital .PFX</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Senha da Certidão</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CNPJ Tomador</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>08/04/2026 17:15</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>VALERIA MANEGEMENT</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>53656846000140</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>./dados/sao_paulo/certidoes/VALERIA CRISTINA DE PADUA.pfx</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Valeria2026</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>33.512.889/0001-45</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>09/04/2026 14:29</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>53656846000140</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>CAROLINA</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>11735236000192</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>./dados/sao_paulo/certidoes/CAROLINA BARROS.pfx</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Carolina2025</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>54.536.709/0001-35</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>09/04/2026 14:33</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="6">
-        <v>11735236000192</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>MANA CONSULTORIA</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>22121066000172</v>
       </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>./dados/sao_paulo/certidoes/PAULO HENRIQUE WODEWOTZKY LTDA_60720594000137.pfx</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Paulo2025</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>60720594000137</v>
       </c>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="E5" s="6"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="E6" s="6"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E7" s="6"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E8" s="6"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E9" s="6"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E10" s="6"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E15" s="6"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.click: Timeout 30000ms exceeded.
+Call log:
+  - waiting for locator("#btnCertificado")
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="E7" s="6" t="n"/>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="E8" s="6" t="n"/>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="E9" s="6" t="n"/>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="6" t="n"/>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="E11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="E12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="E13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="E15" s="6" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>